--- a/gene_panel.xlsx
+++ b/gene_panel.xlsx
@@ -64,7 +64,7 @@
     <t>Gene Aliases</t>
   </si>
   <si>
-    <t>F</t>
+    <t>ABL1</t>
   </si>
   <si>
     <t>ENST00000318560</t>
